--- a/public/exports-60-250/29189757.xlsx
+++ b/public/exports-60-250/29189757.xlsx
@@ -6064,7 +6064,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
